--- a/Compititor's_Price/Recticel_Prices/Recticel_Prices_23-06-2026.xlsx
+++ b/Compititor's_Price/Recticel_Prices/Recticel_Prices_23-06-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Documents\Price_Comp_Dashboard\Compititor's_Price\Recticel_Prices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DA124CD-D104-4A41-96CF-272B0D4A7C5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B993D7D8-B75F-4510-8B3A-5496A6B39097}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="37770" yWindow="1950" windowWidth="21600" windowHeight="11550" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="269">
   <si>
     <t>SKU</t>
   </si>
@@ -809,6 +809,24 @@
   </si>
   <si>
     <t>£49.50</t>
+  </si>
+  <si>
+    <t>£49.61</t>
+  </si>
+  <si>
+    <t>£59.61</t>
+  </si>
+  <si>
+    <t>£60.64</t>
+  </si>
+  <si>
+    <t>£59.79</t>
+  </si>
+  <si>
+    <t>£161.40</t>
+  </si>
+  <si>
+    <t>£131.38</t>
   </si>
 </sst>
 </file>
@@ -1890,7 +1908,7 @@
         <v>175</v>
       </c>
       <c r="O13" t="s">
-        <v>28</v>
+        <v>263</v>
       </c>
       <c r="P13" t="s">
         <v>28</v>
@@ -1946,7 +1964,7 @@
         <v>165</v>
       </c>
       <c r="O14" t="s">
-        <v>28</v>
+        <v>264</v>
       </c>
       <c r="P14" t="s">
         <v>28</v>
@@ -2002,7 +2020,7 @@
         <v>186</v>
       </c>
       <c r="O15" t="s">
-        <v>28</v>
+        <v>265</v>
       </c>
       <c r="P15" t="s">
         <v>28</v>
@@ -2058,7 +2076,7 @@
         <v>253</v>
       </c>
       <c r="O16" t="s">
-        <v>28</v>
+        <v>266</v>
       </c>
       <c r="P16" t="s">
         <v>28</v>
@@ -2170,7 +2188,7 @@
         <v>254</v>
       </c>
       <c r="O18" t="s">
-        <v>28</v>
+        <v>267</v>
       </c>
       <c r="P18" t="s">
         <v>28</v>
@@ -2226,7 +2244,7 @@
         <v>255</v>
       </c>
       <c r="O19" t="s">
-        <v>28</v>
+        <v>268</v>
       </c>
       <c r="P19" t="s">
         <v>28</v>
